--- a/survey_templates/035_t_shirt_survey--survey_templates.xlsx
+++ b/survey_templates/035_t_shirt_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'x-large'}</t>
+          <t>x-large</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'X-Large'}</t>
+          <t>X-Large</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'casual'}</t>
+          <t>casual</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Casual'}</t>
+          <t>Casual</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'formal'}</t>
+          <t>formal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Formal'}</t>
+          <t>Formal</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sporty'}</t>
+          <t>sporty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sporty'}</t>
+          <t>Sporty</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'boho'}</t>
+          <t>boho</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Boho'}</t>
+          <t>Boho</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'gray'}</t>
+          <t>gray</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Gray'}</t>
+          <t>Gray</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cotton'}</t>
+          <t>cotton</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cotton'}</t>
+          <t>Cotton</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'polyester'}</t>
+          <t>polyester</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Polyester'}</t>
+          <t>Polyester</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'linen'}</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Linen'}</t>
+          <t>Linen</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'logo'}</t>
+          <t>logo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Logo'}</t>
+          <t>Logo</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pattern'}</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pattern'}</t>
+          <t>Pattern</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'solid'}</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Solid'}</t>
+          <t>Solid</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'crew'}</t>
+          <t>crew</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Crew'}</t>
+          <t>Crew</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'v-neck'}</t>
+          <t>v-neck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'V-Neck'}</t>
+          <t>V-Neck</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'crew-neck'}</t>
+          <t>crew-neck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Crew-Neck'}</t>
+          <t>Crew-Neck</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'zipper'}</t>
+          <t>zipper</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Zipper'}</t>
+          <t>Zipper</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pocketless'}</t>
+          <t>pocketless</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pocketless'}</t>
+          <t>Pocketless</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rolled'}</t>
+          <t>rolled</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rolled'}</t>
+          <t>Rolled</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'tab'}</t>
+          <t>tab</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Tab'}</t>
+          <t>Tab</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bottom'}</t>
+          <t>bottom</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bottom'}</t>
+          <t>Bottom</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sleeve'}</t>
+          <t>sleeve</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sleeve'}</t>
+          <t>Sleeve</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hem'}</t>
+          <t>hem</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hem'}</t>
+          <t>Hem</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'wide'}</t>
+          <t>wide</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Wide'}</t>
+          <t>Wide</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'narrow'}</t>
+          <t>narrow</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Narrow'}</t>
+          <t>Narrow</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'simple'}</t>
+          <t>simple</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Simple'}</t>
+          <t>Simple</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'decorative'}</t>
+          <t>decorative</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Decorative'}</t>
+          <t>Decorative</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'front'}</t>
+          <t>front</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Front'}</t>
+          <t>Front</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'back'}</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Back'}</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'crew'}</t>
+          <t>crew</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Crew'}</t>
+          <t>Crew</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'v-neck'}</t>
+          <t>v-neck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'V-Neck'}</t>
+          <t>V-Neck</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'crew-neck'}</t>
+          <t>crew-neck</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Crew-Neck'}</t>
+          <t>Crew-Neck</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'wide'}</t>
+          <t>wide</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Wide'}</t>
+          <t>Wide</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'narrow'}</t>
+          <t>narrow</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Narrow'}</t>
+          <t>Narrow</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full'}</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full'}</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bottom'}</t>
+          <t>bottom</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bottom'}</t>
+          <t>Bottom</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'top'}</t>
+          <t>top</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Top'}</t>
+          <t>Top</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'wide'}</t>
+          <t>wide</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Wide'}</t>
+          <t>Wide</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'narrow'}</t>
+          <t>narrow</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Narrow'}</t>
+          <t>Narrow</t>
         </is>
       </c>
     </row>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'simple'}</t>
+          <t>simple</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Simple'}</t>
+          <t>Simple</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'decorative'}</t>
+          <t>decorative</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Decorative'}</t>
+          <t>Decorative</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'simple'}</t>
+          <t>simple</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Simple'}</t>
+          <t>Simple</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'decorative'}</t>
+          <t>decorative</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Decorative'}</t>
+          <t>Decorative</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'t-shirt'}</t>
+          <t>t-shirt</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'T-Shirt'}</t>
+          <t>T-Shirt</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'polo_shirt'}</t>
+          <t>polo_shirt</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Polo Shirt'}</t>
+          <t>Polo Shirt</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'tank_top'}</t>
+          <t>tank_top</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Tank Top'}</t>
+          <t>Tank Top</t>
         </is>
       </c>
     </row>
